--- a/光伏配储项目/电价数据/2026/凤凰站.xlsx
+++ b/光伏配储项目/电价数据/2026/凤凰站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55362</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.52017</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.86364</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.1269</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.02166</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.9208999999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.7223200000000001</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.7317</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.53996</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.59216</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.52555</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.69452</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.68503</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.5188400000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.7118300000000001</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.70233</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.66603</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.69102</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.52899</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.70508</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.54765</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.7031799999999999</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.71092</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.73594</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.82535</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.85862</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.67703</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.67218</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45252</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.73422</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7569400000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.01066</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.9952000000000001</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.08613</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.7505700000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.69836</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50126</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40657</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40846</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.78371</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.95047</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.31299</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52319</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7602300000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.7681399999999999</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74778</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9286799999999999</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.89518</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.0484</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.3158</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.12473</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.12415</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7343500000000001</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.16947</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09688</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22911</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.53503</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.10662</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24797</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.47663</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.3057</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.23642</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.41105</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.35452</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.28523</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.80359</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.16851</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.0372</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17655</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51264</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.61551</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.51578</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.5898300000000001</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.48789</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.52496</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.50589</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.5159400000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.51591</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.50589</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.51189</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.5609400000000001</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.77132</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.0765</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.84124</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.5932000000000001</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48688</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.5402100000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45992</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.51013</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.9355</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.15119</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.7763</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.11994</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03796</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.9874700000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.70812</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54802</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5670299999999999</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.67996</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.15466</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.23164</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47579</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15885</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.62986</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.0787</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.81851</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.25161</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.13652</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28339</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62171</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63859</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.57021</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.16181</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16897</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17761</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.17213</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9689500000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20232</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19406</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66899</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.16216</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20562</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.21151</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.50785</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.41316</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16841</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.5094</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26403</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74337</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7647999999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91531</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41315</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.60439</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.6871499999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6959099999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.53403</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.57925</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.50917</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.84751</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.5918099999999999</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.5601699999999999</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.55949</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.48959</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.5877</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.48958</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.57721</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.5250199999999999</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.55888</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.49844</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.5139400000000001</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.50068</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.51061</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.46369</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.6930499999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83086</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10812</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.8739</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7452000000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.70331</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64288</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.72942</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16466</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6773400000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16727</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.62196</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.18783</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.1657</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.7930700000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.94023</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16465</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.16604</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.89246</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5595399999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47468</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67432</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16587</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.02885</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.16513</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.39363</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23665</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.16636</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21581</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20952</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.40217</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.26921</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28612</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64881</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.17225</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.17493</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.78518</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.0396</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07879</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09965</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.08572</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.20511</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16861</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24892</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.9954299999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75454</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.71111</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53032</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.11076</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.72402</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.7168600000000001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.21245</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6823400000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.85629</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.54262</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.62208</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.2399</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.59616</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.52681</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.65785</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.5901799999999999</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.51935</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.5129400000000001</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.45946</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.51213</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.52412</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.5806699999999999</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.49644</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.46153</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.49033</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.67653</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.71837</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.9328200000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16822</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30956</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8383999999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.55194</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66592</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9037500000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.86511</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16436</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43984</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77269</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.95377</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.20558</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.6894600000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.1223</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48534</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.65449</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.9965900000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10295</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.24931</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16894</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.06175</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.9823200000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02583</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.98978</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.25248</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.44167</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.79342</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.34914</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.24543</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.19189</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.84787</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07461</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.16127</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12173</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.15456</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.2552</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31859</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15458</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.26999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18796</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18611</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18896</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18982</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17534</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.15289</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17618</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72419</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5228700000000001</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7264700000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32162</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74371</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49368</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47779</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50463</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.5230900000000001</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45559</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.71658</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.8479099999999999</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.6149199999999999</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70177</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.72682</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.84546</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70526</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55083</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.54987</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5386</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59245</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47068</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08558</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26874</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48232</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5123099999999999</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46633</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.6334500000000001</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.50237</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48321</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48336</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48749</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.59449</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.5055500000000001</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50593</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40868</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48607</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3439</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.19139</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.96646</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9822799999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5904199999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.64867</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.54769</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.5307200000000001</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.5465399999999999</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.51593</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.5146799999999999</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.69136</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.53018</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.53049</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.51339</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.51423</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.5149600000000001</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26889</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07338</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04537</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27269</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08284</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12874</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04499</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04696</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00294</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04674</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0459</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04665</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04629</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26921</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44595</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.5949500000000001</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.5416299999999999</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.5632699999999999</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.5434099999999999</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.54264</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55893</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27019</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28547</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7420099999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.87478</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.67496</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6489299999999999</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6677799999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.74885</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.9398</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48073</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.7302000000000001</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.7319</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.88828</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.63217</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.53598</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48254</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08559</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73182</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72858</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.63901</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.7286900000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7887000000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78284</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.60054</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7419199999999999</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01825</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40654</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.84338</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.43435</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.2985</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.7890499999999999</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.38103</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.0453</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.40131</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76567</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44427</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7745700000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8004</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78504</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50199</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4114</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46011</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21851</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54123</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.61812</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.58587</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.5663899999999999</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.57487</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.58141</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.5829299999999999</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.47109</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.49385</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.48239</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.54453</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.5169400000000001</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.52047</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.51712</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.5171</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.5522899999999999</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.5180800000000001</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.47306</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.49388</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56369</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6662400000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07965</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6386900000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50275</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.56937</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59865</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00153</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33905</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30669</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27475</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.55928</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80171</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5730499999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.6509400000000001</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55071</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.9569</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.77674</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72584</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.64227</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5755</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.98951</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.93375</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.79006</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.54269</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.6720700000000001</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.59065</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.6718999999999999</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.62325</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.70626</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.64167</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.6628500000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.58362</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5780299999999999</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.66091</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.6778500000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.6244500000000001</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.6716599999999999</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.68979</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.76163</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.68062</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.7586799999999999</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.68968</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.68747</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.68896</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.6732899999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.66306</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.62164</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.6622400000000001</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.6060599999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.54567</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.60922</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.5580900000000001</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5825499999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.5595399999999999</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.54508</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.5348999999999999</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.47044</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.57717</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.61217</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62495</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.68286</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.53713</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.55077</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.50213</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.52685</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.49388</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.6420800000000001</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.51339</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.61787</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7281</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.8718400000000001</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.11233</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.93228</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5452899999999999</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11357</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.84404</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9497899999999999</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8597</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.6399600000000001</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.81021</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06792</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.5714199999999999</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52261</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.87554</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.99714</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.54508</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.19141</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.78416</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8138200000000001</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.7426</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7401</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47518</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44325</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49952</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19621</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.5127</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.79332</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7494</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.16646</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.92161</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64336</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.6695</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.70097</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55534</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16423</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61276</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.90947</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.57723</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.57588</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.33771</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.26221</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.23003</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.34681</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.0095</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.5194</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6023200000000001</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.85922</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50613</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.75049</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07609</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07406</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9069400000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.98303</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.93667</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17422</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15472</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8629199999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.15597</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60802</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.9709800000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01618</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.1554</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.95085</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.99113</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58503</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.92457</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.98187</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.08941</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.8859600000000001</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.87359</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79385</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09694</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55671</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.96038</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.9917899999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.74353</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3318</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.61065</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.49326</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.4963399999999999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.50861</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.44677</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.55164</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.59473</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.48232</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.49641</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.49104</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.5341399999999999</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83311</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.71445</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.55271</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.5697000000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.73395</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.8649600000000001</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.57187</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.5759500000000001</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.5777100000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.5125599999999999</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.51235</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.56001</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.62056</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.56463</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.57177</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.4554</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.45137</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.46144</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.67743</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54355</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.51232</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.51406</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.50764</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.51098</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.56853</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.47071</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.5749500000000001</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.53127</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.53776</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.52511</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.5516</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.51716</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.44082</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.50464</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.52581</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.53146</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.52639</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.47501</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45734</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5541900000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28154</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47014</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48518</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7012699999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62767</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8489800000000001</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27142</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16635</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85217</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70139</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.94021</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16792</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12163</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01851</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54186</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44603</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41325</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56326</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.46387</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.46098</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.50645</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.44292</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.48671</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.51118</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.50961</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.58196</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.7267899999999999</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.06427</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.11522</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.99134</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.98007</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98161</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56578</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54729</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94625</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08618</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78441</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.0132</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.76841</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64898</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64172</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.70902</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79996</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.2984</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.8488300000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.4385</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.5715800000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.2332</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.05985</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.7281</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62442</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.65806</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67143</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.66649</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64347</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66796</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20688</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70089</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78269</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.6982</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70598</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71413</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63365</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74843</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02163</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13141</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69204</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70048</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69425</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77388</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72404</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8134199999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.66673</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.4631</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.06755</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.58186</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45875</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.4916</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34416</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.45311</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.6018300000000001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.17873</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.4789</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.50424</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.49247</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.4655899999999999</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.51291</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.50473</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.4997799999999999</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.45793</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7473</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49508</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51081</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.51906</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45221</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92263</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47508</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18005</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90223</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7631699999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49764</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48997</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44876</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7468899999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42626</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.68157</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49603</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5661900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45386</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66487</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6517999999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.52543</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.49048</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.48556</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.71056</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.44282</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42901</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.5164299999999999</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54601</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76146</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76815</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48005</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54653</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7230800000000001</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7625700000000001</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55422</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50183</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.0205</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48714</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44683</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09481</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12977</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08371</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11233</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.1288</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.0186</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19439</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14266</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13186</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17437</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84139</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19128</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8484400000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34116</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90377</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73284</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.7577200000000001</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94897</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.70345</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.39449</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.56473</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.5446</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.53355</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.53992</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.75618</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.37282</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.35744</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42731</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.5195700000000001</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.61946</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.61372</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.53237</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.5146799999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.5801499999999999</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.59592</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.59704</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.51998</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.59176</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.53438</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.58043</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.50703</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.46348</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47099</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.47095</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.5052099999999999</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.43044</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5003299999999999</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45722</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.63988</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5488999999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6851</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53964</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.02915</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.77401</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74165</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.28024</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.34169</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.71836</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.64182</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.34833</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99499</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59208</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49327</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49474</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.53944</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.58997</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.73375</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.17742</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.69129</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.91295</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6650499999999999</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.93459</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.8809600000000001</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74521</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71451</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17565</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17683</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.42563</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23681</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.61729</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20554</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28296</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07779</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.39954</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03332</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.67152</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.64173</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.14099</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.63401</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47333</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.50604</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45228</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44891</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48301</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.4050299999999999</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.52561</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53199</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.8007000000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.66876</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.64998</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50848</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.06835</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.66713</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66335</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.79606</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04956</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.16775</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49948</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19239</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5460199999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15341</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5567300000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57169</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.47885</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45937</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50097</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51128</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46053</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43145</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5384099999999999</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.51558</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.5973200000000001</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.75646</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12779</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.6910599999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.55616</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43189</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.4932</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45509</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44766</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44503</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.5808099999999999</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44803</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46208</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44893</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46317</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5455800000000001</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44611</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45968</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46766</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.49633</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.47978</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.48448</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50248</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.46414</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.37029</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.86395</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.48675</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.42319</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.44573</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.43431</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.43399</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23341</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26708</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11263</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.70038</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17439</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09943</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.68865</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.55899</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49193</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.49814</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41348</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80231</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46579</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48445</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09339</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.36636</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.85184</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8090700000000001</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52179</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7533300000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75198</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51196</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41569</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42436</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41325</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44146</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55431</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44199</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.51251</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.74837</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.57502</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.79744</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45269</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7531599999999999</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52289</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28797</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.29134</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.21769</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.06197</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.95492</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.28503</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.6115900000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5446</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49143</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5755800000000001</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7500399999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5460199999999999</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5413300000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21438</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.75302</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75141</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.57535</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49191</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.98605</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.75974</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.61854</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7505700000000001</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17339</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.60092</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.72758</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.62448</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.23716</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.87402</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.85945</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.88091</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.8995</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15338</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.63906</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9321900000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.67923</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.9572000000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.62054</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.63867</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.7363</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.62101</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79318</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24425</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03425</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.99639</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.00874</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.51522</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.34135</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.04828</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7540800000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34524</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55687</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80138</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.54977</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75103</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75282</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5591</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46887</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42808</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42653</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62778</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5904400000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.55659</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47358</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49471</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.55723</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.1541</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11949</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03239</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12221</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.72622</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.72097</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04323</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.0616</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.66873</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55544</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56191</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5500900000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47727</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46483</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54645</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55138</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54123</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65722</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54195</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04351</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.6543</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54671</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49706</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49759</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49758</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48037</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5748300000000001</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5551</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5586100000000001</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51168</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49844</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5584600000000001</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6571900000000001</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15287</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.05586</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6584</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15115</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.86372</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.65766</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.14073</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.81348</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49251</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5096700000000001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49718</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5328999999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34434</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.71394</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.58305</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.58965</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.7309600000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5529400000000001</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.45228</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62586</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5835199999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.6299</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00527</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17577</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92448</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.96185</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.01077</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.9519</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.91827</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.9481799999999999</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.93206</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.9154500000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9177799999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.67313</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.02823</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.67001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.02511</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.12662</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10848</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.6995399999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.92237</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.8432200000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.91011</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.5419</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.66729</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68977</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73817</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.78823</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.19717</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.07729</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.0168</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.32935</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01245</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11153</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91592</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.7519600000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.75121</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8135399999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.69209</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69068</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.68841</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.72496</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.68526</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.74725</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69538</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46109</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.73342</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5198200000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50557</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.9950599999999999</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.8921699999999999</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.0083</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.8970499999999999</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01611</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.99895</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.99913</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.16676</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06838</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.09336</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.43016</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.66588</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5961900000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.71836</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7054</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.0256</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.69842</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.75145</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13515</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.23316</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.43446</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.20303</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.36517</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.9865900000000001</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.40305</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.38231</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.74596</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.65666</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.42416</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.42597</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.8075800000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.75549</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.8020900000000001</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.5620299999999999</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.42461</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.7542000000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49803</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.81096</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31346</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00394</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9340599999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.96028</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03403</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16263</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06228</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.8642799999999999</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6934199999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.22311</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20886</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.20953</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15177</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86754</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09713</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10806</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10809</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13446</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10579</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5206000000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.2011</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.64055</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57784</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.7319600000000001</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18514</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.86227</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06612</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.03355</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.05126</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03639</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06913</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12812</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.0506</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.0612</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18419</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16275</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21648</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20333</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26738</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16942</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14405</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12001</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.10065</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12679</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.1765</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19408</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17466</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.67452</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.61494</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5485399999999999</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44885</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53132</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31358</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31079</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06772</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.43142</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.44257</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43688</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.43977</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.42263</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40563</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84834</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.5668800000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.6844</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.70004</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.6516799999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.9418500000000001</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.75288</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.94721</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15897</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30704</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44634</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43442</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45938</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54654</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.2528</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85119</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7335499999999999</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7006</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.5028</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.8443200000000001</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.86702</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.2158</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.7733099999999999</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5799299999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58075</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.62774</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.70823</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.5839500000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7358</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.61074</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.20042</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17695</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41154</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17834</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17898</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18431</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10444</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07916</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20742</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.10683</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19313</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05179</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08325</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20649</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08348</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54273</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8041</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56402</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.21422</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84911</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8496</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5545599999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56257</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51547</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539299999999999</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52119</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50122</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49519</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5477799999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5204500000000001</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55757</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17561</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88298</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49391</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17229</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50938</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.56947</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84421</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7951900000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.8528600000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.5010899999999999</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5228400000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54377</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17759</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70098</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55533</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17413</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54922</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55033</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5807599999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79959</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5550499999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7990499999999999</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8490700000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.1742</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7986599999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6835399999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05309</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17609</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17758</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.82411</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73261</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.64551</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.67703</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6850499999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73124</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83475</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81797</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6155700000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.80708</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.75675</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13698</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.75136</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6094400000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.63689</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6387</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.61736</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61463</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7043400000000001</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67095</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8142699999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.7040700000000001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.6081299999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
